--- a/Reports/Stage-1-Test-Report.xlsx
+++ b/Reports/Stage-1-Test-Report.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Full suite on branch stage-1 (HEAD 59addeb plus Task 14 documents), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. No phone or browser check was done; features that only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
+          <t>Full suite on branch stage-1 after the final fix wave (final whole-branch review findings and parked items fixed), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. No phone or browser check was done; features that only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C293)</f>
+        <f>COUNTA('Test Results'!C2:C305)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E293,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E305,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E293,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E305,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E293,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E305,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>lists users with pagination and a text filter on email or name</t>
+          <t>a user suspended before having a profile cannot create one and publish it (409)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>creates and updates a category per language</t>
+          <t>lists users with pagination and a text filter on email or name</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>creates a page and publishes it</t>
+          <t>creates and updates a category per language</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>sets a staff role by email; an unknown email is 404</t>
+          <t>creates a page and publishes it</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>providers are readable; a Reviewer deletes a photo (object removed, published profile photo unpublishes)</t>
+          <t>sets a staff role by email; an unknown email is 404</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GET /me returns the staff user; unknown resources are 404</t>
+          <t>providers are readable; a Reviewer deletes a photo (object removed, published profile photo unpublishes)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot decide their own document</t>
+          <t>GET /me returns the staff user; unknown resources are 404</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension is not counted by the suspended filter</t>
+          <t>a Reviewer cannot decide their own document</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -934,17 +934,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
+          <t>an expired suspension is not counted by the suspended filter</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot change or delete an existing category or page</t>
+          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer can read users and documents</t>
+          <t>a Reviewer cannot change or delete an existing category or page</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
+          <t>a Reviewer can read users and documents</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>the last Administrator cannot be demoted</t>
+          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
+          <t>the last Administrator cannot be demoted</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1096,17 +1096,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>the owner-connection check catches a bypass (negative fixture)</t>
+          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/app-api exports handlers built with appRequest</t>
+          <t>the owner-connection check catches a bypass (negative fixture)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1150,17 +1150,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>first contact creates the users row</t>
+          <t>every route file under app/app-api exports handlers built with appRequest</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>a forged cookie is 401 and touches nothing</t>
+          <t>first contact creates the users row</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>required auth without a cookie is 401</t>
+          <t>a forged cookie is 401 and touches nothing</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>optional auth without a cookie runs with no user</t>
+          <t>required auth without a cookie is 401</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>a handler error rolls back and returns 500</t>
+          <t>optional auth without a cookie runs with no user</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>a body over maxBodyBytes is 413 before the handler runs</t>
+          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>user A cannot read user B through the wrapper</t>
+          <t>a handler error rolls back and returns 500</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot write staff columns of its own row</t>
+          <t>a body over maxBodyBytes is 413 before the handler runs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>first contact with a changed email updates the row</t>
+          <t>user A cannot read user B through the wrapper</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>a second id with the same email gets 409 and no row is written</t>
+          <t>app_user cannot write staff columns of its own row</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>a thrown 400 Response is returned unchanged</t>
+          <t>first contact with a changed email updates the row</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Sign-up and session</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>auth-cookie-flow.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>auth cookie flow / signs up by REST, captures the cookie, and the cookie authenticates /app-api/v1/me</t>
+          <t>a second id with the same email gets 409 and no row is written</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1474,17 +1474,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
+          <t>a thrown 400 Response is returned unchanged</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1501,17 +1501,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Sign-up and session</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>auth-cookie-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>an unknown language is 400</t>
+          <t>signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1528,17 +1528,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>concurrency.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
+          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1555,17 +1555,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>migrates an empty database and classifies every table</t>
+          <t>an unknown language is 400</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1582,17 +1582,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>concurrency.int.spec.ts</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>approval: one email in the user language with the document name and the deep link</t>
+          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1609,17 +1609,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
+          <t>migrates an empty database and classifies every table</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>without a key it only logs and records, and never throws</t>
+          <t>approval: one email in the user language with the document name and the deep link</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
+          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>an unexpected stored language falls back to German</t>
+          <t>without a key it only logs and records, and never throws</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1717,17 +1717,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
+          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1744,17 +1744,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: the object is deleted only after the commit</t>
+          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1771,17 +1771,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>private_files and documents are isolated (RLS)</t>
+          <t>an unexpected stored language falls back to German</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>at most 10 unsubmitted uploads per user (409)</t>
+          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
+          <t>afterCommit: the object is deleted only after the commit</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>EXIF is stripped from the stored JPEG</t>
+          <t>private_files and documents are isolated (RLS)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>alt over 200 characters is 400</t>
+          <t>at most 10 unsubmitted uploads per user (409)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>an unauthenticated upload is refused before the body is read</t>
+          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>the body is read before the first-contact user row and the transaction exist</t>
+          <t>EXIF is stripped from the stored JPEG</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>photos of a published provider are public, and unreadable once suspended</t>
+          <t>alt over 200 characters is 400</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>replacing the profile photo of a published profile works</t>
+          <t>an unauthenticated upload is refused before the body is read</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
+          <t>the body is read before the first-contact user row and the transaction exist</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
+          <t>photos of a published provider are public, and unreadable once suspended</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>the database refuses a second pending check for a requirement</t>
+          <t>replacing the profile photo of a published profile works</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>approval (staff SQL) makes a service with required documents offerable</t>
+          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
+          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2149,17 +2149,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
+          <t>the database refuses a second pending check for a requirement</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2176,17 +2176,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>a new profile photo replaces the old one and deletes its object</t>
+          <t>approval (staff SQL) makes a service with required documents offerable</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2203,17 +2203,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
+          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>a photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
+          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>deleting a photo: another user gets 404, the owner 204 and the object is gone; the profile photo is cleared</t>
+          <t>a new profile photo replaces the old one and deletes its object</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>the profile photo of a published profile cannot be deleted (409)</t>
+          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>photo_id is domain-only and photos are isolated</t>
+          <t>a photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
+          <t>deleting a photo: another user gets 404, the owner 204 and the object is gone; the profile photo is cleared</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>a failed file insert removes the uploaded object</t>
+          <t>the profile photo of a published profile cannot be deleted (409)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
+          <t>photo_id is domain-only and photos are isolated</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2419,17 +2419,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>home page / is German by default: headline, categories, store badges without links, no forbidden words</t>
+          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2446,17 +2446,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>home page / switches to English with ?lang=en and falls back to German for unknown values</t>
+          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2473,17 +2473,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>home page / has per-language metadata with canonical and hreflang for every language</t>
+          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2500,17 +2500,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>site layout / metadataBase makes canonical and hreflang absolute on the site url</t>
+          <t>staff open an image document through the same signed link; it is served as an image</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2527,17 +2527,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>site layout / html lang follows the request language; unknown falls back to de</t>
+          <t>a failed file insert removes the uploaded object</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2554,17 +2554,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>site layout / footer links the four legal pages with catalogue labels in both languages</t>
+          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2581,17 +2581,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
+          <t>is German by default: headline, categories, store badges without links, no forbidden words</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2608,17 +2608,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>two interleaved requests keep their own user id and role</t>
+          <t>switches to English with ?lang=en and falls back to German for unknown values</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2635,17 +2635,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>pages tables / every table is classified (pages and page_texts are public reference tables)</t>
+          <t>has per-language metadata with canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2662,17 +2662,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>pages tables / anonymous app requests read pages but cannot write them</t>
+          <t>metadataBase makes canonical and hreflang absolute on the site url</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2689,17 +2689,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>getPage / returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
+          <t>html lang follows the request language; unknown falls back to de</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2716,17 +2716,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>getPage / publishedPages lists published pages only</t>
+          <t>footer links the four legal pages with catalogue labels in both languages</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2743,17 +2743,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug / renders the Markdown body in both languages with the de fallback</t>
+          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2770,17 +2770,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug / 404 for unknown and unpublished slugs</t>
+          <t>two interleaved requests keep their own user id and role</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug / metadata: title, canonical and hreflang for every language</t>
+          <t>every table is classified (pages and page_texts are public reference tables)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug / escapes HTML in a body and drops unsafe links</t>
+          <t>anonymous app requests read pages but cannot write them</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown / escapes raw html and keeps Markdown</t>
+          <t>returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown / external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
+          <t>publishedPages lists published pages only</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2905,17 +2905,17 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>imports the German file and looks up 01053 Dresden</t>
+          <t>renders the Markdown body in both languages with the de fallback</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2932,17 +2932,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>rejects a four-digit German code and an unknown one</t>
+          <t>404 for unknown and unpublished slugs</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2959,17 +2959,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Berlin to Munich is about 504 km</t>
+          <t>metadata: title, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2986,17 +2986,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>public provider page / German default: headline, public name, category, price "ab 80,00 €", on request, place</t>
+          <t>escapes HTML in a body and drops unsafe links</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3013,17 +3013,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>public provider page / English with ?lang=en: "from €80.00"</t>
+          <t>escapes raw html and keeps Markdown</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3040,17 +3040,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>public provider page / escapes user content</t>
+          <t>external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3067,17 +3067,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>public provider page / 404 for a hidden provider (draft) and an unknown slug</t>
+          <t>imports the German file and looks up 01053 Dresden</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3094,17 +3094,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>public provider page / metadata: title, description, canonical and hreflang for every language</t>
+          <t>rejects a four-digit German code and an unknown one</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3121,17 +3121,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>translate link / is shown only when the texts are not in the page language</t>
+          <t>Berlin to Munich is about 504 km</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>translate link / ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
+          <t>German default: headline, public name, category, price "ab 80,00 €", on request, place</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>translate link / ?translate=1 without a key shows the original texts and the unavailable copy</t>
+          <t>English with ?lang=en: "from €80.00"</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>translate link / translate=1 on texts already in the viewer language: original, no label, no model call</t>
+          <t>escapes user content</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GET is null when there is no profile</t>
+          <t>404 for a hidden provider (draft) and an unknown slug</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3256,17 +3256,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
+          <t>metadata: title, description, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3283,17 +3283,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>an unknown postcode is 400 and changes nothing</t>
+          <t>is shown only when the texts are not in the page language</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3310,17 +3310,17 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>first save needs displayName and providerType; a business needs a business name</t>
+          <t>?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3337,17 +3337,17 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>status, slug and suspended in the body are ignored</t>
+          <t>?translate=1 without a key shows the original texts and the unavailable copy</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3364,17 +3364,17 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>one user's profile is not visible to another</t>
+          <t>translate=1 on texts already in the viewer language: original, no label, no model call</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>an invalid body is 400 with the contract error</t>
+          <t>GET is null when there is no profile</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3418,17 +3418,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
+          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -3445,17 +3445,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>404 when not visible: unknown, draft, or no offerable service</t>
+          <t>an unknown postcode is 400 and changes nothing</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3472,17 +3472,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>a draft page is a 404 for its own owner too</t>
+          <t>first save needs displayName and providerType; a business needs a business name</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -3499,17 +3499,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>unknown language is 400</t>
+          <t>status, slug and suspended in the body are ignored</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3526,17 +3526,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>returns translated texts in the page shape</t>
+          <t>one user's profile is not visible to another</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>a draft or suspended provider -&gt; 404, no call</t>
+          <t>an invalid body is 400 with the contract error</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>unknown lang -&gt; 400</t>
+          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3607,17 +3607,17 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>service failure -&gt; 503 and nothing stored</t>
+          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3634,17 +3634,17 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>a logged-in caller is counted under the user id</t>
+          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -3661,17 +3661,17 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>the provider endpoint reports translatable per viewer language</t>
+          <t>404 when not visible: unknown, draft, or no offerable service</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -3688,17 +3688,17 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>accepts no text from the client</t>
+          <t>a draft page is a 404 for its own owner too</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -3715,17 +3715,17 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
+          <t>unknown language is 400</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3742,17 +3742,17 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>/admin and below go through the auth middleware</t>
+          <t>returns translated texts in the page shape</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
+          <t>a draft or suspended provider -&gt; 404, no call</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3796,17 +3796,17 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>publicNameFor: business name, else first name and surname initial</t>
+          <t>unknown lang -&gt; 400</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3823,17 +3823,17 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>slugify transliterates umlauts and strips the rest</t>
+          <t>service failure -&gt; 503 and nothing stored</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3850,17 +3850,17 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>public name and slug are unique and stable</t>
+          <t>a logged-in caller is counted under the user id</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -3877,17 +3877,17 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
+          <t>the provider endpoint reports translatable per viewer language</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3904,17 +3904,17 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>a postcode-less profile is refused unless it works remotely</t>
+          <t>accepts no text from the client</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -3931,17 +3931,17 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>a suspended profile cannot publish (409)</t>
+          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3958,17 +3958,17 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
+          <t>/admin and below go through the auth middleware</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -3985,17 +3985,17 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
+          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4012,17 +4012,17 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>RLS: set_provider_* touch only the caller's own profile</t>
+          <t>publicNameFor: business name, else first name and surname initial</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4039,17 +4039,17 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>RLS: documents are private and the verdict is staff-only</t>
+          <t>slugify transliterates umlauts and strips the rest</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4066,17 +4066,17 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds: services whose required documents are all approved</t>
+          <t>public name and slug are unique and stable</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>an active admin passes</t>
+          <t>an individual without an account name gets a slug from the display name, never "profile"</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4120,17 +4120,17 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>a suspended admin gets 403</t>
+          <t>first contact copies the account name from the session; a later contact does not overwrite it</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4147,17 +4147,17 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension no longer blocks</t>
+          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4174,17 +4174,17 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
+          <t>a postcode-less profile is refused unless it works remotely</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4201,17 +4201,17 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>another user cannot insert a service or a reference for my provider</t>
+          <t>a suspended profile cannot publish (409)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4228,17 +4228,17 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>the owner cannot move a service to another provider</t>
+          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4255,17 +4255,17 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
+          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4282,17 +4282,17 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>slugify strips accents</t>
+          <t>RLS: set_provider_* touch only the caller's own profile</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4309,17 +4309,17 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot read a private table row of another user</t>
+          <t>RLS: documents are private and the verdict is staff-only</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4336,17 +4336,17 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>public reference tables are readable by app_user and not writable</t>
+          <t>offerableServiceIds: services whose required documents are all approved</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -4363,17 +4363,17 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>radius edge and remote providers</t>
+          <t>an active admin passes</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -4390,17 +4390,17 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>a remote provider more than 200 km away is found, without a distance</t>
+          <t>a suspended admin gets 403</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4417,17 +4417,17 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>a draft is invisible to its owner too</t>
+          <t>an expired suspension no longer blocks</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -4444,17 +4444,17 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
+          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -4471,17 +4471,17 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>a draft, a suspended or a provider without an offerable service never appears</t>
+          <t>another user cannot insert a service or a reference for my provider</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4498,17 +4498,17 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>category filter and q (public name and skills, case-insensitive)</t>
+          <t>the owner cannot move a service to another provider</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4525,17 +4525,17 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
+          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4552,17 +4552,17 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>paging: 20 per page and hasMore</t>
+          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4579,17 +4579,17 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
+          <t>slugify strips accents</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4606,17 +4606,17 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>postcode import upserts: a second run leaves the same count</t>
+          <t>app_user cannot read a private table row of another user</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4633,17 +4633,17 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>the dev guard needs the dev branch AND the dev database host</t>
+          <t>public reference tables are readable by app_user and not writable</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4660,17 +4660,17 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
+          <t>radius edge and remote providers</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4687,17 +4687,17 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
+          <t>a remote provider more than 200 km away is found, without a distance</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4714,17 +4714,17 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
+          <t>a draft is invisible to its owner too</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4741,17 +4741,17 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>neonAuth retries a 429, then succeeds</t>
+          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4768,17 +4768,17 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>neonAuth signs in when the email already exists</t>
+          <t>a draft, a suspended or a provider without an offerable service never appears</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4795,17 +4795,17 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
+          <t>category filter and q (public name and skills, case-insensitive)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4822,17 +4822,17 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>a service needs a profile first (409)</t>
+          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -4849,17 +4849,17 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>create, list and patch a service; shapes fit the contract</t>
+          <t>paging: 20 per page and hasMore</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -4876,17 +4876,17 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>on-request has no price, even when one is sent</t>
+          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -4903,17 +4903,17 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>bad service input: no price, three decimals, unknown category are 400</t>
+          <t>postcode import upserts: a second run leaves the same count</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -4930,17 +4930,17 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>a service in a category with required documents waits for approval</t>
+          <t>the dev guard needs the dev branch AND the dev database host</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -4957,17 +4957,17 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>user A cannot edit or delete user B's service</t>
+          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -4984,17 +4984,17 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>references are capped at 2 (409), can be patched and deleted</t>
+          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5011,17 +5011,17 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>providers sitemap lists only visible providers</t>
+          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5038,17 +5038,17 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>pages sitemap lists the home page and published pages only</t>
+          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5065,17 +5065,17 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
+          <t>neonAuth retries a 429, then succeeds</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5092,17 +5092,17 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Smoke test</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>smoke.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>connects to the test database and sees PostGIS</t>
+          <t>neonAuth signs in when the email already exists</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5119,17 +5119,17 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Test database guard</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>test-guard.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>the test guard refuses a non-local or non-test URL</t>
+          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5146,17 +5146,17 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>translate / stores translations and serves the second request from the store without a call</t>
+          <t>a service needs a profile first (409)</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -5173,17 +5173,17 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>translate / an edited text is re-translated, the rest comes from the store</t>
+          <t>create, list and patch a service; shapes fit the contract</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5200,17 +5200,17 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>translate / texts already in the target language are returned unchanged without a call</t>
+          <t>on-request has no price, even when one is sent</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -5227,17 +5227,17 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>translate / a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
+          <t>bad service input: no price, three decimals, unknown category are 400</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -5254,17 +5254,17 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>translate / a non-2xx answer throws TranslationUnavailable</t>
+          <t>a service in a category with required documents waits for approval</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -5281,17 +5281,17 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>translate / line breaks survive</t>
+          <t>user A cannot edit or delete user B's service</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -5308,17 +5308,17 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>translate / no key -&gt; TranslationUnavailable without a call</t>
+          <t>references are capped at 2 (409), can be patched and deleted</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -5335,17 +5335,17 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>translate / the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
+          <t>providers sitemap lists only visible providers</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -5362,17 +5362,17 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>translate / the limit boundary: the 30th call passes, the 31st is refused</t>
+          <t>pages sitemap lists the home page and published pages only</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -5389,17 +5389,17 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>translate / a timeout -&gt; TranslationUnavailable</t>
+          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -5416,17 +5416,17 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Smoke test</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>smoke.int.spec.ts</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>translate / concurrent translations of the same page store one row per text</t>
+          <t>connects to the test database and sees PostGIS</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -5443,17 +5443,17 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Test database guard</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>test-guard.int.spec.ts</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>translate / writes through the request transaction and commits with it</t>
+          <t>the test guard refuses a non-local or non-test URL</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>translate / the default timeout is 12 seconds</t>
+          <t>stores translations and serves the second request from the store without a call</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>translate / French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
+          <t>an edited text is re-translated, the rest comes from the store</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>translate / a page the detector cannot classify is translated when long enough, left alone when short</t>
+          <t>texts already in the target language are returned unchanged without a call</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>translate / a German profile of short skills and titles needs no translation for de but does for en</t>
+          <t>a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>translate / a Markdown-fenced answer parses; the request carries max_tokens</t>
+          <t>a non-2xx answer throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>translate / an empty string from the model stores nothing</t>
+          <t>line breaks survive</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>translate / counter rows older than 24 hours are deleted; recent ones stay</t>
+          <t>no key -&gt; TranslationUnavailable without a call</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>translate / anonymous client keys are salted hashes, never the raw IP</t>
+          <t>the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>translate / textsOf picks the translatable fields of a profile</t>
+          <t>the limit boundary: the 30th call passes, the 31st is refused</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>translate / needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
+          <t>a timeout -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>translation tables are insert-only for app_user / anonymous callers can insert and read, never update or delete</t>
+          <t>concurrent translations of the same page store one row per text</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -5767,22 +5767,22 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>writes through the request transaction and commits with it</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -5794,22 +5794,22 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>the default timeout is 12 seconds</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -5821,22 +5821,22 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -5848,22 +5848,22 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>a page the detector cannot classify is translated when long enough, left alone when short</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -5875,22 +5875,22 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>a German profile of short skills and titles needs no translation for de but does for en</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -5902,22 +5902,22 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>a Markdown-fenced answer parses; the request carries max_tokens</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>an empty string from the model stores nothing</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -5956,22 +5956,22 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>counter rows older than 24 hours are deleted; recent ones stay</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -5983,22 +5983,22 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>anonymous client keys are salted hashes, never the raw IP</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -6010,22 +6010,22 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>textsOf picks the translatable fields of a profile</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -6037,22 +6037,22 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -6064,22 +6064,22 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>anonymous callers can insert and read, never update or delete</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>updateUserName changes the name on the auth account</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>updateUserName changes the name on the auth account</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>updateName saves the account name in both places and updates the session user; a failure keeps the old one</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded → police-certificate none</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>updateName saves the account name in both places and updates the session user; a failure keeps the old one</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -7419,12 +7419,12 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>a babysitting service with nothing uploaded → police-certificate none</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>profile validation mirrors the server limits</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>profile body clears empty fields and drops business fields for private providers</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>the account name is not part of the profile body; the form pre-fills it from the session user</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>strengths are a list in the form and one per line on the server</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>cancelled is null</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>cancelled is null</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>profile validation mirrors the server limits</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>profile body clears empty fields and drops business fields for private providers</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>the account name is not part of the profile body; the form pre-fills it from the session user</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8062,22 +8062,22 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>rejects three decimals and negative prices</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
@@ -8089,22 +8089,22 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>needs no price on request</t>
+          <t>strengths are a list in the form and one per line on the server</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -8116,22 +8116,22 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>caps pageSize at 100</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
@@ -8143,22 +8143,22 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>parseBody answers 400 with the issues</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -8170,22 +8170,22 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>parseQuery reads the search params</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
@@ -8197,22 +8197,22 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>lists are { docs: [...] }</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -8224,22 +8224,22 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>contract/index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>reference year is checked against the current year at parse time</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
@@ -8251,22 +8251,22 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>de and en have the same keys</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -8278,22 +8278,22 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>no text is empty and no two keys of one namespace carry the same text</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
@@ -8305,22 +8305,22 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -8332,22 +8332,22 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>the product name is only written in brand.name</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
@@ -8359,22 +8359,22 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>Shared packages</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>replaces placeholders and falls back to the key when missing</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>contract/index.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>fills the brand name without a parameter</t>
+          <t>rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>contract/index.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>knows its languages</t>
+          <t>needs no price on request</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>i18n/index.test.ts</t>
+          <t>contract/index.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>formats per language</t>
+          <t>caps pageSize at 100</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8472,20 +8472,344 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
+          <t>contract/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>parseBody answers 400 with the issues</t>
+        </is>
+      </c>
+      <c r="D293" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>contract/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>parseQuery reads the search params</t>
+        </is>
+      </c>
+      <c r="D294" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>contract/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>lists are { docs: [...] }</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>contract/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>reference year is checked against the current year at parse time</t>
+        </is>
+      </c>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
           <t>i18n/index.test.ts</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr">
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>de and en have the same keys</t>
+        </is>
+      </c>
+      <c r="D297" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>no text is empty and no two keys of one namespace carry the same text</t>
+        </is>
+      </c>
+      <c r="D298" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>the product name is only written in brand.name</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>replaces placeholders and falls back to the key when missing</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>fills the brand name without a parameter</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>knows its languages</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>formats per language</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>Shared packages</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>i18n/index.test.ts</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
         <is>
           <t>formats price labels from the catalogue</t>
         </is>
       </c>
-      <c r="D293" s="4" t="inlineStr">
+      <c r="D305" s="4" t="inlineStr">
         <is>
           <t>Packages</t>
         </is>
       </c>
-      <c r="E293" s="4" t="inlineStr">
+      <c r="E305" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -8617,7 +8941,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>191 tests.</t>
+          <t>203 tests.</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8985,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Evidence: apps/mobile/src/api/auth.test.ts, hooks/use-session.test.ts; apps/web/tests/auth-cookie-flow.int.spec.ts (cookie authenticates /app-api/v1/me). Screens still need a phone run.</t>
+          <t>Evidence: apps/mobile/src/api/auth.test.ts, hooks/use-session.test.ts; apps/web/tests/auth-cookie-flow.int.spec.ts (a real sign-up cookie reaches /app-api/v1/me, which answers 403 until the email is confirmed). Screens still need a phone run.</t>
         </is>
       </c>
     </row>
@@ -8871,7 +9195,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Upload verification documents and see their status.</t>
+          <t>Upload verification documents (PDF, or a JPEG, PNG or WEBP scan or photo) and see their status.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -8881,7 +9205,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Evidence: apps/web/tests/files-review.int.spec.ts; apps/mobile/src/lib/documents.test.ts. Picking a file from OneDrive needs a phone run.</t>
+          <t>Evidence: apps/web/tests/files.int.spec.ts (PDF, JPEG, PNG and WEBP accepted and stored with their own type; GIF and text refused; staff link to an image document), files-review.int.spec.ts; apps/mobile/src/lib/documents.test.ts. Fixed in the final fix wave: images were refused before (only PDF). Scan, gallery and OneDrive picking need a phone run.</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9200,12 +9524,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Still to come after Task 14.</t>
+          <t>Done (final-review.md): 0 Critical, 3 Important, 10 Minor. All Important and 8 Minor fixed in the final fix wave (commits 65be850 to d68d4d0); the other 2 Minor are deferred to the South Africa work (see README Known gaps).</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9217,12 +9541,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>packages/db/src/seed/guard.ts: an empty NEON_DEV_ENDPOINT_ID disables the host check (every host contains an empty string). Should use ||.</t>
+          <t>Fixed in ebfccdd: an empty value now falls back to the dev endpoint (seeds.int.spec.ts checks it).</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Before next seed change</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9234,12 +9558,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>A rerun after a crash during the placeholder photo upload can create the services a second time.</t>
+          <t>Fixed in d68d4d0: a provider that already has services skips adding them again (seeds.int.spec.ts checks it).</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9251,12 +9575,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Hit its 5 second timeout once; passed in the 27 October full run.</t>
+          <t>Fixed in d68d4d0: the import test now has 30 seconds.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -9376,6 +9700,210 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Final review I-1: suspension bypass</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>A user suspended before having a profile could create one and publish it. Fixed in 65be850 (migration 0008; admin-api.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Final review I-2: unconfirmed emails</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>The app API now refuses accounts whose email is not confirmed (403). Fixed in 70403fb (provider-profile, app-request and auth-cookie-flow specs).</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Final review I-3: image documents</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>JPEG, PNG and WEBP documents are accepted next to PDF, cleaned of metadata. Fixed in 7b7c342 (files.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-1: two-language switches</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Language lookups use the language list and the default language. Fixed in 39055cc.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-2: fixed currency and postcode length</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Currency read from the service; postcode length left to the country lookup. Fixed in 172c21a.</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-3: empty account name</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Slug falls back to the display name; the first contact copies the account name. Fixed in 4a7e9d7 (public-name.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-4: empty DATABASE_URL_UNPOOLED</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Migrations, imports and seeds fall back to DATABASE_URL. Fixed in ebfccdd.</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-5: email outbox in production</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Without RESEND_API_KEY one log line, no text, nothing kept. Fixed in 56ee8e3 (email.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-6: seeds section of the deployment notes</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Corrected, including ALLOW_PRODUCTION=1 at cutover. Fixed in the docs commit of the final fix wave.</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-7: PATCH /me body check</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Checked with MePatchSchema from the contract. Fixed in fdd6ba2 (provider-profile.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-8: eligibility for hidden providers</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Answers only for a visible provider or the caller's own. Fixed in 65be850 (rls-providers.int.spec.ts).</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Final review M-9 and M-10: German legal links, two-language switch on the website</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Footer legal links and the website language switch assume Germany and two languages. Deferred to the South Africa work.</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>South Africa work</t>
         </is>
       </c>
     </row>

--- a/Reports/Stage-1-Test-Report.xlsx
+++ b/Reports/Stage-1-Test-Report.xlsx
@@ -9711,7 +9711,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>A user suspended before having a profile could create one and publish it. Fixed in 65be850 (migration 0008; admin-api.int.spec.ts).</t>
+          <t>A user suspended before having a profile could create one and publish it. Fixed in 65be850 (function set_provider_published in packages/db/src/rls.ts; admin-api.int.spec.ts).</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">

--- a/Reports/Stage-1-Test-Report.xlsx
+++ b/Reports/Stage-1-Test-Report.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C305)</f>
+        <f>COUNTA('Test Results'!C2:C306)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E305,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E306,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E305,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E306,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E305,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E306,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8810,6 +8810,33 @@
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Seeds</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>seeds.int.spec.ts</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -8941,7 +8968,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>203 tests.</t>
+          <t>204 tests (203 at the final fix wave; one seed-data test added 27 October).</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9507,12 +9534,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>NEON_AUTH_BASE_URL and NEON_AUTH_COOKIE_SECRET are not yet added to the KANDO GitHub repository, so CI cannot run the web tests.</t>
+          <t>Optional: without NEON_AUTH_BASE_URL and NEON_AUTH_COOKIE_SECRET the one test against the real Neon Auth is skipped in CI. CI is green without them.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner, optional</t>
         </is>
       </c>
     </row>
@@ -9904,6 +9931,108 @@
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>South Africa work</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CI: categories seed test failed on GitHub</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Counted all categories; other spec files leave their own behind in the shared CI database. Counts only the seeded slugs now. Fixed in 67c80bb; CI green since.</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Seed account list out of git (owner request, 27 October)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>The 14 test accounts, their password and made-up profiles were in packages/domain/src/seed/test-users.ts in a public repository. Now read from the git-ignored seed-data/test-users.json; a one-customer-one-provider example file is committed; tests use their own fixture. Fixed in a72cf74. Earlier commits still hold the list: squash-merge PR #2 and delete the branch.</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Code review 27 October (mobile build config), 1 of 6: microphone permission</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>The image-picker plugin added android.permission.RECORD_AUDIO and an iOS microphone text by default; the app never records audio. Plugin option microphonePermission=false, hand-written permissions list removed. Resolved config checked: no microphone entry. Fixed in 27ea70c.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Code review 27 October, 2 of 6: production API address</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>The production build profile did not pin EXPO_PUBLIC_API_URL, so a local build could bake in a LAN address. Pinned to https://skillweb.space like the preview profile. Fixed in 27ea70c.</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Code review 27 October, 3 to 5 of 6: dead configuration</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Empty ios.infoPlist, the router asyncRoutes block the plugin overwrites, and the empty submit.production placeholder removed. Fixed in 27ea70c.</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Code review 27 October, 6 of 6: README duplication</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Concerns the old skill-web README only (development-build status repeated in two places). Not applicable to KANDO.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
